--- a/corrected-bank-specimens-for-user/08-scb/parsed-excel/scb statement - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/08-scb/parsed-excel/scb statement - parsed.xlsx
@@ -426,7 +426,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-08T16:17:01.239Z</v>
+        <v>2026-07-14T13:50:04.042Z</v>
       </c>
     </row>
     <row r="5">
